--- a/data_shopify/commandes_shopify_fictif.xlsx
+++ b/data_shopify/commandes_shopify_fictif.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1811"/>
+  <dimension ref="A1:L1968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89831,6 +89831,7699 @@
         </is>
       </c>
     </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>EMY-501811</t>
+        </is>
+      </c>
+      <c r="B1812" s="1" t="n">
+        <v>46293.33402777778</v>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>client9994@example.com</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1812" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1812" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1812" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1812" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1812" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>EMY-501812</t>
+        </is>
+      </c>
+      <c r="B1813" s="1" t="n">
+        <v>46291.54305555556</v>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>client9995@example.com</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1813" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1813" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1813" t="n">
+        <v>518</v>
+      </c>
+      <c r="J1813" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1813" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>EMY-501813</t>
+        </is>
+      </c>
+      <c r="B1814" s="1" t="n">
+        <v>46286.43611111111</v>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>client9996@example.com</t>
+        </is>
+      </c>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1814" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1814" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1814" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1814" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1814" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1814" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>EMY-501814</t>
+        </is>
+      </c>
+      <c r="B1815" s="1" t="n">
+        <v>46283.33680555555</v>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>client9997@example.com</t>
+        </is>
+      </c>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1815" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1815" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1815" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1815" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1815" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>EMY-501815</t>
+        </is>
+      </c>
+      <c r="B1816" s="1" t="n">
+        <v>46276.89166666667</v>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>client9998@example.com</t>
+        </is>
+      </c>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1816" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1816" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1816" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1816" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1816" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1816" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>EMY-501816</t>
+        </is>
+      </c>
+      <c r="B1817" s="1" t="n">
+        <v>46274.71805555555</v>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>client9999@example.com</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1817" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1817" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1817" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1817" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1817" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1817" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>EMY-501817</t>
+        </is>
+      </c>
+      <c r="B1818" s="1" t="n">
+        <v>46284.50902777778</v>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>client10000@example.com</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1818" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1818" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1818" t="n">
+        <v>578</v>
+      </c>
+      <c r="J1818" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1818" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>EMY-501818</t>
+        </is>
+      </c>
+      <c r="B1819" s="1" t="n">
+        <v>46278.6</v>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>client10001@example.com</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1819" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1819" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1819" t="n">
+        <v>42</v>
+      </c>
+      <c r="I1819" t="n">
+        <v>42</v>
+      </c>
+      <c r="J1819" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1819" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>EMY-501819</t>
+        </is>
+      </c>
+      <c r="B1820" s="1" t="n">
+        <v>46280.83472222222</v>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>client10002@example.com</t>
+        </is>
+      </c>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1820" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1820" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1820" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1820" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1820" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1820" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>EMY-501820</t>
+        </is>
+      </c>
+      <c r="B1821" s="1" t="n">
+        <v>46279.72986111111</v>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>client10003@example.com</t>
+        </is>
+      </c>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1821" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1821" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1821" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1821" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1821" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1821" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>EMY-501821</t>
+        </is>
+      </c>
+      <c r="B1822" s="1" t="n">
+        <v>46281.77569444444</v>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>client10004@example.com</t>
+        </is>
+      </c>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1822" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1822" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1822" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1822" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1822" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1822" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>EMY-501822</t>
+        </is>
+      </c>
+      <c r="B1823" s="1" t="n">
+        <v>46274.83819444444</v>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>client10005@example.com</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1823" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1823" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1823" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1823" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1823" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>EMY-501823</t>
+        </is>
+      </c>
+      <c r="B1824" s="1" t="n">
+        <v>46289.48263888889</v>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>client10006@example.com</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1824" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1824" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1824" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1824" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1824" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1824" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1824" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>EMY-501824</t>
+        </is>
+      </c>
+      <c r="B1825" s="1" t="n">
+        <v>46276.47708333333</v>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>client10007@example.com</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1825" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1825" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1825" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1825" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1825" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1825" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>EMY-501825</t>
+        </is>
+      </c>
+      <c r="B1826" s="1" t="n">
+        <v>46276.86111111111</v>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>client10008@example.com</t>
+        </is>
+      </c>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1826" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1826" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1826" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1826" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1826" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1826" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>EMY-501826</t>
+        </is>
+      </c>
+      <c r="B1827" s="1" t="n">
+        <v>46273.68055555555</v>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>client10009@example.com</t>
+        </is>
+      </c>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1827" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1827" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1827" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1827" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1827" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1827" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1827" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>EMY-501827</t>
+        </is>
+      </c>
+      <c r="B1828" s="1" t="n">
+        <v>46275.77152777778</v>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>client10010@example.com</t>
+        </is>
+      </c>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1828" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1828" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1828" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1828" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1828" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1828" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1828" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>EMY-501828</t>
+        </is>
+      </c>
+      <c r="B1829" s="1" t="n">
+        <v>46281.66319444445</v>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>client10011@example.com</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1829" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1829" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1829" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1829" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1829" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1829" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>EMY-501829</t>
+        </is>
+      </c>
+      <c r="B1830" s="1" t="n">
+        <v>46287.89791666667</v>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>client10012@example.com</t>
+        </is>
+      </c>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1830" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1830" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1830" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1830" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1830" t="n">
+        <v>438</v>
+      </c>
+      <c r="J1830" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1830" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>EMY-501830</t>
+        </is>
+      </c>
+      <c r="B1831" s="1" t="n">
+        <v>46273.36458333334</v>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>client10013@example.com</t>
+        </is>
+      </c>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1831" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1831" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1831" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1831" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1831" t="n">
+        <v>438</v>
+      </c>
+      <c r="J1831" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1831" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>EMY-501831</t>
+        </is>
+      </c>
+      <c r="B1832" s="1" t="n">
+        <v>46279.63055555556</v>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>client10014@example.com</t>
+        </is>
+      </c>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1832" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1832" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1832" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1832" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1832" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1832" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1832" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>EMY-501832</t>
+        </is>
+      </c>
+      <c r="B1833" s="1" t="n">
+        <v>46276.3625</v>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>client10015@example.com</t>
+        </is>
+      </c>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1833" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1833" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1833" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1833" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1833" t="n">
+        <v>578</v>
+      </c>
+      <c r="J1833" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1833" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>EMY-501833</t>
+        </is>
+      </c>
+      <c r="B1834" s="1" t="n">
+        <v>46274.57361111111</v>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>client10016@example.com</t>
+        </is>
+      </c>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1834" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1834" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1834" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1834" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1834" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1834" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>EMY-501834</t>
+        </is>
+      </c>
+      <c r="B1835" s="1" t="n">
+        <v>46281.59375</v>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>client10017@example.com</t>
+        </is>
+      </c>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1835" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1835" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1835" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1835" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1835" t="n">
+        <v>358</v>
+      </c>
+      <c r="J1835" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1835" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>EMY-501835</t>
+        </is>
+      </c>
+      <c r="B1836" s="1" t="n">
+        <v>46280.39305555556</v>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>client10018@example.com</t>
+        </is>
+      </c>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1836" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1836" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1836" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1836" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1836" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1836" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>EMY-501836</t>
+        </is>
+      </c>
+      <c r="B1837" s="1" t="n">
+        <v>46287.47708333333</v>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>client10019@example.com</t>
+        </is>
+      </c>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1837" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1837" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1837" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1837" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1837" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1837" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>EMY-501837</t>
+        </is>
+      </c>
+      <c r="B1838" s="1" t="n">
+        <v>46274.69930555556</v>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>client10020@example.com</t>
+        </is>
+      </c>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1838" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1838" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1838" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1838" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1838" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1838" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>EMY-501838</t>
+        </is>
+      </c>
+      <c r="B1839" s="1" t="n">
+        <v>46274.62847222222</v>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>client10021@example.com</t>
+        </is>
+      </c>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1839" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1839" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1839" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1839" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1839" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1839" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>EMY-501839</t>
+        </is>
+      </c>
+      <c r="B1840" s="1" t="n">
+        <v>46291.66805555556</v>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>client10022@example.com</t>
+        </is>
+      </c>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1840" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1840" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1840" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1840" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1840" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1840" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>EMY-501840</t>
+        </is>
+      </c>
+      <c r="B1841" s="1" t="n">
+        <v>46280.47569444445</v>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>client10023@example.com</t>
+        </is>
+      </c>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1841" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1841" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1841" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1841" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1841" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1841" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>EMY-501841</t>
+        </is>
+      </c>
+      <c r="B1842" s="1" t="n">
+        <v>46292.67083333333</v>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>client10024@example.com</t>
+        </is>
+      </c>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1842" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1842" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1842" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1842" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1842" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1842" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1842" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>EMY-501842</t>
+        </is>
+      </c>
+      <c r="B1843" s="1" t="n">
+        <v>46282.39444444444</v>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>client10025@example.com</t>
+        </is>
+      </c>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1843" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1843" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1843" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1843" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1843" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1843" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>EMY-501843</t>
+        </is>
+      </c>
+      <c r="B1844" s="1" t="n">
+        <v>46294.37222222222</v>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>client10026@example.com</t>
+        </is>
+      </c>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1844" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1844" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1844" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1844" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1844" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1844" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>EMY-501844</t>
+        </is>
+      </c>
+      <c r="B1845" s="1" t="n">
+        <v>46295.50902777778</v>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>client10027@example.com</t>
+        </is>
+      </c>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1845" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1845" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1845" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1845" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1845" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1845" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>EMY-501845</t>
+        </is>
+      </c>
+      <c r="B1846" s="1" t="n">
+        <v>46293.57847222222</v>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>client10028@example.com</t>
+        </is>
+      </c>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1846" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1846" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1846" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1846" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1846" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1846" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>EMY-501846</t>
+        </is>
+      </c>
+      <c r="B1847" s="1" t="n">
+        <v>46295.56597222222</v>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>client10029@example.com</t>
+        </is>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1847" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1847" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1847" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1847" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1847" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1847" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>EMY-501847</t>
+        </is>
+      </c>
+      <c r="B1848" s="1" t="n">
+        <v>46277.54722222222</v>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>client10030@example.com</t>
+        </is>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1848" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1848" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1848" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1848" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1848" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1848" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>EMY-501848</t>
+        </is>
+      </c>
+      <c r="B1849" s="1" t="n">
+        <v>46290.91319444445</v>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>client10031@example.com</t>
+        </is>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1849" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1849" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1849" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1849" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1849" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1849" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>EMY-501849</t>
+        </is>
+      </c>
+      <c r="B1850" s="1" t="n">
+        <v>46273.40763888889</v>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>client10032@example.com</t>
+        </is>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1850" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1850" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1850" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1850" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1850" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1850" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>EMY-501850</t>
+        </is>
+      </c>
+      <c r="B1851" s="1" t="n">
+        <v>46295.35</v>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>client10033@example.com</t>
+        </is>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1851" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1851" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1851" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1851" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1851" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1851" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1851" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>EMY-501851</t>
+        </is>
+      </c>
+      <c r="B1852" s="1" t="n">
+        <v>46280.32083333333</v>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>client10034@example.com</t>
+        </is>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1852" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1852" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1852" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1852" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1852" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1852" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1852" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>EMY-501852</t>
+        </is>
+      </c>
+      <c r="B1853" s="1" t="n">
+        <v>46283.29652777778</v>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>client10035@example.com</t>
+        </is>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1853" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1853" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1853" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1853" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1853" t="n">
+        <v>438</v>
+      </c>
+      <c r="J1853" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1853" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>EMY-501853</t>
+        </is>
+      </c>
+      <c r="B1854" s="1" t="n">
+        <v>46286.68888888889</v>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>client10036@example.com</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1854" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1854" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1854" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1854" t="n">
+        <v>74</v>
+      </c>
+      <c r="J1854" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1854" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>EMY-501854</t>
+        </is>
+      </c>
+      <c r="B1855" s="1" t="n">
+        <v>46294.78263888889</v>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>client10037@example.com</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1855" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1855" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1855" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1855" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1855" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1855" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>EMY-501855</t>
+        </is>
+      </c>
+      <c r="B1856" s="1" t="n">
+        <v>46294.83819444444</v>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>client10038@example.com</t>
+        </is>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1856" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1856" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1856" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1856" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1856" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1856" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1856" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>EMY-501856</t>
+        </is>
+      </c>
+      <c r="B1857" s="1" t="n">
+        <v>46277.43472222222</v>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>client10039@example.com</t>
+        </is>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1857" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1857" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1857" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1857" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1857" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1857" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1857" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>EMY-501857</t>
+        </is>
+      </c>
+      <c r="B1858" s="1" t="n">
+        <v>46282.46736111111</v>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>client10040@example.com</t>
+        </is>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1858" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1858" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1858" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1858" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1858" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1858" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1858" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>EMY-501858</t>
+        </is>
+      </c>
+      <c r="B1859" s="1" t="n">
+        <v>46288.83125</v>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>client10041@example.com</t>
+        </is>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1859" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1859" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1859" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1859" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1859" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1859" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1859" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>EMY-501859</t>
+        </is>
+      </c>
+      <c r="B1860" s="1" t="n">
+        <v>46275.86666666667</v>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>client10042@example.com</t>
+        </is>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1860" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1860" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1860" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1860" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1860" t="n">
+        <v>398</v>
+      </c>
+      <c r="J1860" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1860" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>EMY-501860</t>
+        </is>
+      </c>
+      <c r="B1861" s="1" t="n">
+        <v>46275.60138888889</v>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>client10043@example.com</t>
+        </is>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1861" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1861" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1861" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1861" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1861" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1861" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1861" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>EMY-501861</t>
+        </is>
+      </c>
+      <c r="B1862" s="1" t="n">
+        <v>46276.81041666667</v>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>client10044@example.com</t>
+        </is>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1862" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1862" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1862" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1862" t="n">
+        <v>42</v>
+      </c>
+      <c r="I1862" t="n">
+        <v>42</v>
+      </c>
+      <c r="J1862" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1862" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>EMY-501862</t>
+        </is>
+      </c>
+      <c r="B1863" s="1" t="n">
+        <v>46277.81180555555</v>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>client10045@example.com</t>
+        </is>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1863" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1863" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1863" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1863" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1863" t="n">
+        <v>37</v>
+      </c>
+      <c r="J1863" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1863" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>EMY-501863</t>
+        </is>
+      </c>
+      <c r="B1864" s="1" t="n">
+        <v>46286.87361111111</v>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>client10046@example.com</t>
+        </is>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1864" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1864" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1864" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1864" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1864" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1864" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1864" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>EMY-501864</t>
+        </is>
+      </c>
+      <c r="B1865" s="1" t="n">
+        <v>46289.61111111111</v>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>client10047@example.com</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1865" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1865" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1865" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1865" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1865" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1865" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1865" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>EMY-501865</t>
+        </is>
+      </c>
+      <c r="B1866" s="1" t="n">
+        <v>46277.38472222222</v>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>client10048@example.com</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1866" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1866" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1866" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1866" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1866" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1866" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1866" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>EMY-501866</t>
+        </is>
+      </c>
+      <c r="B1867" s="1" t="n">
+        <v>46274.45347222222</v>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>client10049@example.com</t>
+        </is>
+      </c>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1867" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1867" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1867" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1867" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1867" t="n">
+        <v>90</v>
+      </c>
+      <c r="J1867" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1867" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>EMY-501867</t>
+        </is>
+      </c>
+      <c r="B1868" s="1" t="n">
+        <v>46288.30694444444</v>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>client10050@example.com</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1868" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1868" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1868" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1868" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1868" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1868" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1868" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>EMY-501868</t>
+        </is>
+      </c>
+      <c r="B1869" s="1" t="n">
+        <v>46288.42847222222</v>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>client10051@example.com</t>
+        </is>
+      </c>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1869" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1869" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1869" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1869" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1869" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1869" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1869" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>EMY-501869</t>
+        </is>
+      </c>
+      <c r="B1870" s="1" t="n">
+        <v>46277.69027777778</v>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>client10052@example.com</t>
+        </is>
+      </c>
+      <c r="D1870" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1870" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1870" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1870" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1870" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1870" t="n">
+        <v>578</v>
+      </c>
+      <c r="J1870" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1870" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>EMY-501870</t>
+        </is>
+      </c>
+      <c r="B1871" s="1" t="n">
+        <v>46278.30277777778</v>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>client10053@example.com</t>
+        </is>
+      </c>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1871" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1871" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1871" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1871" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1871" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1871" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1871" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>EMY-501871</t>
+        </is>
+      </c>
+      <c r="B1872" s="1" t="n">
+        <v>46281.83680555555</v>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>client10054@example.com</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1872" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1872" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1872" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1872" t="n">
+        <v>37</v>
+      </c>
+      <c r="J1872" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1872" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>EMY-501872</t>
+        </is>
+      </c>
+      <c r="B1873" s="1" t="n">
+        <v>46273.425</v>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>client10055@example.com</t>
+        </is>
+      </c>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1873" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1873" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1873" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1873" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1873" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1873" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1873" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>EMY-501873</t>
+        </is>
+      </c>
+      <c r="B1874" s="1" t="n">
+        <v>46318.49236111111</v>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>client10056@example.com</t>
+        </is>
+      </c>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1874" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1874" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1874" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1874" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1874" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1874" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1874" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>EMY-501874</t>
+        </is>
+      </c>
+      <c r="B1875" s="1" t="n">
+        <v>46314.33263888889</v>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>client10057@example.com</t>
+        </is>
+      </c>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1875" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1875" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1875" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1875" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1875" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1875" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1875" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>EMY-501875</t>
+        </is>
+      </c>
+      <c r="B1876" s="1" t="n">
+        <v>46299.78402777778</v>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>client10058@example.com</t>
+        </is>
+      </c>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1876" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1876" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1876" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1876" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1876" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1876" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1876" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>EMY-501876</t>
+        </is>
+      </c>
+      <c r="B1877" s="1" t="n">
+        <v>46298.65347222222</v>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>client10059@example.com</t>
+        </is>
+      </c>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1877" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1877" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1877" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1877" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1877" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1877" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1877" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>EMY-501877</t>
+        </is>
+      </c>
+      <c r="B1878" s="1" t="n">
+        <v>46309.40694444445</v>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>client10060@example.com</t>
+        </is>
+      </c>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1878" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1878" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1878" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1878" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1878" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1878" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1878" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>EMY-501878</t>
+        </is>
+      </c>
+      <c r="B1879" s="1" t="n">
+        <v>46304.5375</v>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>client10061@example.com</t>
+        </is>
+      </c>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1879" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1879" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1879" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1879" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1879" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1879" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1879" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>EMY-501879</t>
+        </is>
+      </c>
+      <c r="B1880" s="1" t="n">
+        <v>46306.31319444445</v>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>client10062@example.com</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1880" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1880" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1880" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1880" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1880" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1880" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1880" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>EMY-501880</t>
+        </is>
+      </c>
+      <c r="B1881" s="1" t="n">
+        <v>46313.31458333333</v>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>client10063@example.com</t>
+        </is>
+      </c>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1881" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1881" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1881" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1881" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1881" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1881" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1881" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>EMY-501881</t>
+        </is>
+      </c>
+      <c r="B1882" s="1" t="n">
+        <v>46316.77152777778</v>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>client10064@example.com</t>
+        </is>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1882" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1882" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1882" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1882" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1882" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1882" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1882" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>EMY-501882</t>
+        </is>
+      </c>
+      <c r="B1883" s="1" t="n">
+        <v>46307.60763888889</v>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>client10065@example.com</t>
+        </is>
+      </c>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1883" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1883" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1883" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1883" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1883" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1883" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1883" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>EMY-501883</t>
+        </is>
+      </c>
+      <c r="B1884" s="1" t="n">
+        <v>46304.42152777778</v>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>client10066@example.com</t>
+        </is>
+      </c>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1884" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1884" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1884" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1884" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1884" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1884" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1884" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>EMY-501884</t>
+        </is>
+      </c>
+      <c r="B1885" s="1" t="n">
+        <v>46319.59513888889</v>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>client10067@example.com</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1885" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1885" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1885" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1885" t="n">
+        <v>42</v>
+      </c>
+      <c r="I1885" t="n">
+        <v>42</v>
+      </c>
+      <c r="J1885" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1885" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>EMY-501885</t>
+        </is>
+      </c>
+      <c r="B1886" s="1" t="n">
+        <v>46303.50763888889</v>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>client10068@example.com</t>
+        </is>
+      </c>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1886" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1886" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1886" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1886" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1886" t="n">
+        <v>438</v>
+      </c>
+      <c r="J1886" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1886" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>EMY-501886</t>
+        </is>
+      </c>
+      <c r="B1887" s="1" t="n">
+        <v>46316.86666666667</v>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>client10069@example.com</t>
+        </is>
+      </c>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1887" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1887" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1887" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1887" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1887" t="n">
+        <v>37</v>
+      </c>
+      <c r="J1887" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1887" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>EMY-501887</t>
+        </is>
+      </c>
+      <c r="B1888" s="1" t="n">
+        <v>46304.85416666666</v>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>client10070@example.com</t>
+        </is>
+      </c>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1888" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1888" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1888" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1888" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1888" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1888" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1888" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>EMY-501888</t>
+        </is>
+      </c>
+      <c r="B1889" s="1" t="n">
+        <v>46321.67986111111</v>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>client10071@example.com</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1889" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1889" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1889" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1889" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1889" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1889" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1889" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>EMY-501889</t>
+        </is>
+      </c>
+      <c r="B1890" s="1" t="n">
+        <v>46308.62361111111</v>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>client10072@example.com</t>
+        </is>
+      </c>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1890" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1890" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1890" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1890" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1890" t="n">
+        <v>37</v>
+      </c>
+      <c r="J1890" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1890" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>EMY-501890</t>
+        </is>
+      </c>
+      <c r="B1891" s="1" t="n">
+        <v>46326.80069444444</v>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>client10073@example.com</t>
+        </is>
+      </c>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1891" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1891" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1891" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1891" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1891" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1891" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1891" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>EMY-501891</t>
+        </is>
+      </c>
+      <c r="B1892" s="1" t="n">
+        <v>46309.61388888889</v>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>client10074@example.com</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1892" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1892" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1892" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1892" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1892" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1892" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1892" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>EMY-501892</t>
+        </is>
+      </c>
+      <c r="B1893" s="1" t="n">
+        <v>46317.45763888889</v>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>client10075@example.com</t>
+        </is>
+      </c>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1893" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1893" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1893" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1893" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1893" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1893" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1893" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>EMY-501893</t>
+        </is>
+      </c>
+      <c r="B1894" s="1" t="n">
+        <v>46303.71458333333</v>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>client10076@example.com</t>
+        </is>
+      </c>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1894" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1894" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1894" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1894" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1894" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1894" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1894" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>EMY-501894</t>
+        </is>
+      </c>
+      <c r="B1895" s="1" t="n">
+        <v>46325.47777777778</v>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>client10077@example.com</t>
+        </is>
+      </c>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1895" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1895" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1895" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1895" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1895" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1895" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1895" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>EMY-501895</t>
+        </is>
+      </c>
+      <c r="B1896" s="1" t="n">
+        <v>46298.66805555556</v>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>client10078@example.com</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1896" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1896" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1896" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1896" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1896" t="n">
+        <v>74</v>
+      </c>
+      <c r="J1896" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1896" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>EMY-501896</t>
+        </is>
+      </c>
+      <c r="B1897" s="1" t="n">
+        <v>46314.325</v>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>client10079@example.com</t>
+        </is>
+      </c>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1897" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1897" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1897" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1897" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1897" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1897" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1897" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>EMY-501897</t>
+        </is>
+      </c>
+      <c r="B1898" s="1" t="n">
+        <v>46314.56944444445</v>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>client10080@example.com</t>
+        </is>
+      </c>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1898" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1898" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1898" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1898" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1898" t="n">
+        <v>37</v>
+      </c>
+      <c r="J1898" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1898" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>EMY-501898</t>
+        </is>
+      </c>
+      <c r="B1899" s="1" t="n">
+        <v>46306.57222222222</v>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>client10081@example.com</t>
+        </is>
+      </c>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1899" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1899" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1899" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1899" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1899" t="n">
+        <v>518</v>
+      </c>
+      <c r="J1899" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1899" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>EMY-501899</t>
+        </is>
+      </c>
+      <c r="B1900" s="1" t="n">
+        <v>46299.80902777778</v>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>client10082@example.com</t>
+        </is>
+      </c>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1900" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1900" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1900" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1900" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1900" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1900" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1900" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>EMY-501900</t>
+        </is>
+      </c>
+      <c r="B1901" s="1" t="n">
+        <v>46312.52708333333</v>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>client10083@example.com</t>
+        </is>
+      </c>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1901" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1901" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1901" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1901" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1901" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1901" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1901" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>EMY-501901</t>
+        </is>
+      </c>
+      <c r="B1902" s="1" t="n">
+        <v>46324.77152777778</v>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>client10084@example.com</t>
+        </is>
+      </c>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1902" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1902" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1902" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1902" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1902" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1902" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1902" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>EMY-501902</t>
+        </is>
+      </c>
+      <c r="B1903" s="1" t="n">
+        <v>46309.34305555555</v>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>client10085@example.com</t>
+        </is>
+      </c>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1903" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1903" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1903" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1903" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1903" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1903" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1903" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>EMY-501903</t>
+        </is>
+      </c>
+      <c r="B1904" s="1" t="n">
+        <v>46312.76180555556</v>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>client10086@example.com</t>
+        </is>
+      </c>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1904" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1904" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1904" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1904" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1904" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1904" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1904" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>EMY-501904</t>
+        </is>
+      </c>
+      <c r="B1905" s="1" t="n">
+        <v>46312.78888888889</v>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>client10087@example.com</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1905" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1905" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1905" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1905" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1905" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1905" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1905" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>EMY-501905</t>
+        </is>
+      </c>
+      <c r="B1906" s="1" t="n">
+        <v>46319.49513888889</v>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>client10088@example.com</t>
+        </is>
+      </c>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1906" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1906" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1906" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1906" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1906" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1906" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1906" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>EMY-501906</t>
+        </is>
+      </c>
+      <c r="B1907" s="1" t="n">
+        <v>46320.64166666667</v>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>client10089@example.com</t>
+        </is>
+      </c>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1907" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1907" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1907" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1907" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1907" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1907" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1907" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>EMY-501907</t>
+        </is>
+      </c>
+      <c r="B1908" s="1" t="n">
+        <v>46297.53263888889</v>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>client10090@example.com</t>
+        </is>
+      </c>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1908" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1908" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1908" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1908" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1908" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1908" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1908" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>EMY-501908</t>
+        </is>
+      </c>
+      <c r="B1909" s="1" t="n">
+        <v>46311.29722222222</v>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>client10091@example.com</t>
+        </is>
+      </c>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1909" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1909" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1909" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1909" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1909" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1909" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1909" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>EMY-501909</t>
+        </is>
+      </c>
+      <c r="B1910" s="1" t="n">
+        <v>46309.86180555556</v>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>client10092@example.com</t>
+        </is>
+      </c>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1910" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1910" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1910" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1910" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1910" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1910" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1910" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>EMY-501910</t>
+        </is>
+      </c>
+      <c r="B1911" s="1" t="n">
+        <v>46323.74583333333</v>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>client10093@example.com</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1911" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1911" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1911" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1911" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1911" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1911" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1911" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>EMY-501911</t>
+        </is>
+      </c>
+      <c r="B1912" s="1" t="n">
+        <v>46315.34375</v>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>client10094@example.com</t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1912" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1912" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1912" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1912" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1912" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1912" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1912" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>EMY-501912</t>
+        </is>
+      </c>
+      <c r="B1913" s="1" t="n">
+        <v>46310.40555555555</v>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>client10095@example.com</t>
+        </is>
+      </c>
+      <c r="D1913" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1913" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1913" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1913" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1913" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1913" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1913" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1913" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>EMY-501913</t>
+        </is>
+      </c>
+      <c r="B1914" s="1" t="n">
+        <v>46312.56666666667</v>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>client10096@example.com</t>
+        </is>
+      </c>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1914" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1914" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1914" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1914" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1914" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1914" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1914" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>EMY-501914</t>
+        </is>
+      </c>
+      <c r="B1915" s="1" t="n">
+        <v>46311.90069444444</v>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>client10097@example.com</t>
+        </is>
+      </c>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1915" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1915" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1915" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1915" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1915" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1915" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1915" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>EMY-501915</t>
+        </is>
+      </c>
+      <c r="B1916" s="1" t="n">
+        <v>46317.63194444445</v>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>client10098@example.com</t>
+        </is>
+      </c>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1916" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1916" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1916" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1916" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1916" t="n">
+        <v>37</v>
+      </c>
+      <c r="J1916" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1916" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>EMY-501916</t>
+        </is>
+      </c>
+      <c r="B1917" s="1" t="n">
+        <v>46323.46666666667</v>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>client10099@example.com</t>
+        </is>
+      </c>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1917" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1917" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1917" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1917" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1917" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1917" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1917" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>EMY-501917</t>
+        </is>
+      </c>
+      <c r="B1918" s="1" t="n">
+        <v>46296.8625</v>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>client10100@example.com</t>
+        </is>
+      </c>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1918" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1918" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1918" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1918" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1918" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1918" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1918" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>EMY-501918</t>
+        </is>
+      </c>
+      <c r="B1919" s="1" t="n">
+        <v>46322.91458333333</v>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>client10101@example.com</t>
+        </is>
+      </c>
+      <c r="D1919" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1919" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1919" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1919" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1919" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1919" t="n">
+        <v>37</v>
+      </c>
+      <c r="J1919" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1919" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>EMY-501919</t>
+        </is>
+      </c>
+      <c r="B1920" s="1" t="n">
+        <v>46316.37291666667</v>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>client10102@example.com</t>
+        </is>
+      </c>
+      <c r="D1920" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1920" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1920" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1920" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1920" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1920" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1920" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1920" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>EMY-501920</t>
+        </is>
+      </c>
+      <c r="B1921" s="1" t="n">
+        <v>46306.76805555556</v>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>client10103@example.com</t>
+        </is>
+      </c>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1921" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1921" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1921" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1921" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1921" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1921" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1921" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>EMY-501921</t>
+        </is>
+      </c>
+      <c r="B1922" s="1" t="n">
+        <v>46325.85416666666</v>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>client10104@example.com</t>
+        </is>
+      </c>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1922" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1922" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1922" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1922" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1922" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1922" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1922" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>EMY-501922</t>
+        </is>
+      </c>
+      <c r="B1923" s="1" t="n">
+        <v>46323.74027777778</v>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>client10105@example.com</t>
+        </is>
+      </c>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1923" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1923" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1923" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1923" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1923" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1923" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1923" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>EMY-501923</t>
+        </is>
+      </c>
+      <c r="B1924" s="1" t="n">
+        <v>46299.59930555556</v>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>client10106@example.com</t>
+        </is>
+      </c>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1924" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1924" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1924" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1924" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1924" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1924" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1924" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>EMY-501924</t>
+        </is>
+      </c>
+      <c r="B1925" s="1" t="n">
+        <v>46311.31875</v>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>client10107@example.com</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1925" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1925" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1925" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1925" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1925" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1925" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>EMY-501925</t>
+        </is>
+      </c>
+      <c r="B1926" s="1" t="n">
+        <v>46316.54652777778</v>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>client10108@example.com</t>
+        </is>
+      </c>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1926" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1926" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1926" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1926" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1926" t="inlineStr">
+        <is>
+          <t>Publicité Meta/Google</t>
+        </is>
+      </c>
+      <c r="K1926" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>EMY-501926</t>
+        </is>
+      </c>
+      <c r="B1927" s="1" t="n">
+        <v>46308.59930555556</v>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>client10109@example.com</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1927" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1927" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1927" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1927" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1927" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1927" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>EMY-501927</t>
+        </is>
+      </c>
+      <c r="B1928" s="1" t="n">
+        <v>46322.61041666667</v>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>client10110@example.com</t>
+        </is>
+      </c>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1928" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1928" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1928" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1928" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1928" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1928" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1928" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>EMY-501928</t>
+        </is>
+      </c>
+      <c r="B1929" s="1" t="n">
+        <v>46299.72430555556</v>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>client10111@example.com</t>
+        </is>
+      </c>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1929" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1929" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1929" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1929" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1929" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1929" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1929" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>EMY-501929</t>
+        </is>
+      </c>
+      <c r="B1930" s="1" t="n">
+        <v>46298.71736111111</v>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>client10112@example.com</t>
+        </is>
+      </c>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1930" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1930" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1930" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1930" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1930" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1930" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1930" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>EMY-501930</t>
+        </is>
+      </c>
+      <c r="B1931" s="1" t="n">
+        <v>46302.37013888889</v>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>client10113@example.com</t>
+        </is>
+      </c>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1931" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1931" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1931" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1931" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1931" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1931" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1931" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>EMY-501931</t>
+        </is>
+      </c>
+      <c r="B1932" s="1" t="n">
+        <v>46304.83958333333</v>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>client10114@example.com</t>
+        </is>
+      </c>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1932" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1932" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1932" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1932" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1932" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1932" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1932" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>EMY-501932</t>
+        </is>
+      </c>
+      <c r="B1933" s="1" t="n">
+        <v>46321.80208333334</v>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>client10115@example.com</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1933" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1933" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1933" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1933" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1933" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1933" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1933" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>EMY-501933</t>
+        </is>
+      </c>
+      <c r="B1934" s="1" t="n">
+        <v>46311.61736111111</v>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>client10116@example.com</t>
+        </is>
+      </c>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1934" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1934" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1934" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1934" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1934" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1934" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>EMY-501934</t>
+        </is>
+      </c>
+      <c r="B1935" s="1" t="n">
+        <v>46305.61180555556</v>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>client10117@example.com</t>
+        </is>
+      </c>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1935" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1935" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1935" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1935" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1935" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1935" t="inlineStr">
+        <is>
+          <t>Recommandation</t>
+        </is>
+      </c>
+      <c r="K1935" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>EMY-501935</t>
+        </is>
+      </c>
+      <c r="B1936" s="1" t="n">
+        <v>46298.87847222222</v>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>client10118@example.com</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1936" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1936" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1936" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1936" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1936" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1936" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+      <c r="K1936" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>EMY-501936</t>
+        </is>
+      </c>
+      <c r="B1937" s="1" t="n">
+        <v>46308.68958333333</v>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>client10119@example.com</t>
+        </is>
+      </c>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1937" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1937" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1937" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1937" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1937" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1937" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>EMY-501937</t>
+        </is>
+      </c>
+      <c r="B1938" s="1" t="n">
+        <v>46319.84236111111</v>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>client10120@example.com</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1938" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1938" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1938" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1938" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1938" t="n">
+        <v>37</v>
+      </c>
+      <c r="J1938" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1938" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>EMY-501938</t>
+        </is>
+      </c>
+      <c r="B1939" s="1" t="n">
+        <v>46306.55555555555</v>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>client10121@example.com</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1939" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1939" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1939" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1939" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1939" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1939" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1939" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>EMY-501939</t>
+        </is>
+      </c>
+      <c r="B1940" s="1" t="n">
+        <v>46309.36597222222</v>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>client10122@example.com</t>
+        </is>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1940" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1940" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1940" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1940" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1940" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1940" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>EMY-501940</t>
+        </is>
+      </c>
+      <c r="B1941" s="1" t="n">
+        <v>46309.53819444445</v>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>client10123@example.com</t>
+        </is>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1941" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1941" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1941" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1941" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1941" t="inlineStr">
+        <is>
+          <t>Recherche organique</t>
+        </is>
+      </c>
+      <c r="K1941" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>EMY-501941</t>
+        </is>
+      </c>
+      <c r="B1942" s="1" t="n">
+        <v>46249.61597222222</v>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>client6048@example.com</t>
+        </is>
+      </c>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1942" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1942" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1942" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1942" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1942" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1942" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>EMY-501942</t>
+        </is>
+      </c>
+      <c r="B1943" s="1" t="n">
+        <v>46263.75972222222</v>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>client1394@example.com</t>
+        </is>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1943" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1943" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1943" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1943" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1943" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1943" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>EMY-501943</t>
+        </is>
+      </c>
+      <c r="B1944" s="1" t="n">
+        <v>46280.57986111111</v>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>client1500@example.com</t>
+        </is>
+      </c>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1944" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1944" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1944" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1944" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1944" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1944" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>EMY-501944</t>
+        </is>
+      </c>
+      <c r="B1945" s="1" t="n">
+        <v>46292.87777777778</v>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>client6707@example.com</t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1945" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1945" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1945" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1945" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1945" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1945" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>EMY-501945</t>
+        </is>
+      </c>
+      <c r="B1946" s="1" t="n">
+        <v>46297.57291666666</v>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>client9893@example.com</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1946" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1946" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1946" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1946" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1946" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1946" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>EMY-501946</t>
+        </is>
+      </c>
+      <c r="B1947" s="1" t="n">
+        <v>46286.30555555555</v>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>client8741@example.com</t>
+        </is>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1947" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1947" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1947" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1947" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1947" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1947" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>EMY-501947</t>
+        </is>
+      </c>
+      <c r="B1948" s="1" t="n">
+        <v>46302.79027777778</v>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>client2601@example.com</t>
+        </is>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1948" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1948" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1948" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1948" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1948" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1948" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>EMY-501948</t>
+        </is>
+      </c>
+      <c r="B1949" s="1" t="n">
+        <v>46255.56736111111</v>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>client6724@example.com</t>
+        </is>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1949" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1949" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1949" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1949" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1949" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1949" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>EMY-501949</t>
+        </is>
+      </c>
+      <c r="B1950" s="1" t="n">
+        <v>46254.76458333333</v>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>client9388@example.com</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1950" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1950" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1950" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1950" t="n">
+        <v>179</v>
+      </c>
+      <c r="I1950" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1950" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1950" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>EMY-501950</t>
+        </is>
+      </c>
+      <c r="B1951" s="1" t="n">
+        <v>46289.71319444444</v>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>client1905@example.com</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1951" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1951" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1951" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1951" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1951" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1951" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>EMY-501951</t>
+        </is>
+      </c>
+      <c r="B1952" s="1" t="n">
+        <v>46286.78611111111</v>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>client7873@example.com</t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>Éveil</t>
+        </is>
+      </c>
+      <c r="F1952" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1952" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1952" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1952" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1952" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1952" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>EMY-501952</t>
+        </is>
+      </c>
+      <c r="B1953" s="1" t="n">
+        <v>46278.38611111111</v>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>client4521@example.com</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1953" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1953" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1953" t="n">
+        <v>199</v>
+      </c>
+      <c r="I1953" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1953" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1953" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>EMY-501953</t>
+        </is>
+      </c>
+      <c r="B1954" s="1" t="n">
+        <v>46273.82013888889</v>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>client2837@example.com</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1954" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1954" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1954" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1954" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1954" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1954" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>EMY-501954</t>
+        </is>
+      </c>
+      <c r="B1955" s="1" t="n">
+        <v>46293.81666666667</v>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>client3324@example.com</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1955" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1955" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1955" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1955" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1955" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1955" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>EMY-501955</t>
+        </is>
+      </c>
+      <c r="B1956" s="1" t="n">
+        <v>46266.73611111111</v>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>client5654@example.com</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1956" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1956" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1956" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1956" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1956" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1956" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>EMY-501956</t>
+        </is>
+      </c>
+      <c r="B1957" s="1" t="n">
+        <v>46258.39444444444</v>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>client8351@example.com</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>Clarté</t>
+        </is>
+      </c>
+      <c r="F1957" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1957" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1957" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1957" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1957" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1957" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>EMY-501957</t>
+        </is>
+      </c>
+      <c r="B1958" s="1" t="n">
+        <v>46254.80347222222</v>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>client4363@example.com</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1958" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1958" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1958" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1958" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1958" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1958" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>EMY-501958</t>
+        </is>
+      </c>
+      <c r="B1959" s="1" t="n">
+        <v>46250.47847222222</v>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>client5323@example.com</t>
+        </is>
+      </c>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1959" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1959" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1959" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1959" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1959" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1959" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>EMY-501959</t>
+        </is>
+      </c>
+      <c r="B1960" s="1" t="n">
+        <v>46273.46111111111</v>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>client6505@example.com</t>
+        </is>
+      </c>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1960" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1960" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1960" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1960" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1960" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1960" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>EMY-501960</t>
+        </is>
+      </c>
+      <c r="B1961" s="1" t="n">
+        <v>46265.64166666667</v>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>client4980@example.com</t>
+        </is>
+      </c>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>Évasion</t>
+        </is>
+      </c>
+      <c r="F1961" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1961" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1961" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1961" t="n">
+        <v>289</v>
+      </c>
+      <c r="J1961" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1961" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>EMY-501961</t>
+        </is>
+      </c>
+      <c r="B1962" s="1" t="n">
+        <v>46275.62361111111</v>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>client4197@example.com</t>
+        </is>
+      </c>
+      <c r="D1962" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1962" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1962" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1962" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1962" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1962" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1962" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>EMY-501962</t>
+        </is>
+      </c>
+      <c r="B1963" s="1" t="n">
+        <v>46286.6875</v>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>client4067@example.com</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1963" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1963" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1963" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1963" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1963" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1963" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>EMY-501963</t>
+        </is>
+      </c>
+      <c r="B1964" s="1" t="n">
+        <v>46277.83125</v>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>client4181@example.com</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1964" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="G1964" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1964" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1964" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1964" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1964" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>EMY-501964</t>
+        </is>
+      </c>
+      <c r="B1965" s="1" t="n">
+        <v>46291.71597222222</v>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>client7964@example.com</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1965" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1965" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1965" t="n">
+        <v>239</v>
+      </c>
+      <c r="I1965" t="n">
+        <v>239</v>
+      </c>
+      <c r="J1965" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1965" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>EMY-501965</t>
+        </is>
+      </c>
+      <c r="B1966" s="1" t="n">
+        <v>46291.64791666667</v>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>client7964@example.com</t>
+        </is>
+      </c>
+      <c r="D1966" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1966" t="inlineStr">
+        <is>
+          <t>Cocon</t>
+        </is>
+      </c>
+      <c r="F1966" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1966" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1966" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1966" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1966" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1966" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>EMY-501966</t>
+        </is>
+      </c>
+      <c r="B1967" s="1" t="n">
+        <v>46257.55972222222</v>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>client9053@example.com</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>Douceur</t>
+        </is>
+      </c>
+      <c r="F1967" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1967" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1967" t="n">
+        <v>259</v>
+      </c>
+      <c r="I1967" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1967" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1967" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>EMY-501967</t>
+        </is>
+      </c>
+      <c r="B1968" s="1" t="n">
+        <v>46277.81944444445</v>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>client9053@example.com</t>
+        </is>
+      </c>
+      <c r="D1968" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>Sérénité</t>
+        </is>
+      </c>
+      <c r="F1968" t="inlineStr">
+        <is>
+          <t>Diffuseur</t>
+        </is>
+      </c>
+      <c r="G1968" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1968" t="n">
+        <v>219</v>
+      </c>
+      <c r="I1968" t="n">
+        <v>219</v>
+      </c>
+      <c r="J1968" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K1968" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
